--- a/data/用户/管理员教师名单.xlsx
+++ b/data/用户/管理员教师名单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="教师名单" sheetId="1" r:id="rId1"/>
@@ -1295,62 +1295,62 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>

--- a/data/用户/管理员教师名单.xlsx
+++ b/data/用户/管理员教师名单.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>工号</t>
   </si>
@@ -53,6 +53,12 @@
     <t>教师</t>
   </si>
   <si>
+    <t>203045</t>
+  </si>
+  <si>
+    <t>黄晓玲</t>
+  </si>
+  <si>
     <t>206004</t>
   </si>
   <si>
@@ -62,7 +68,7 @@
     <t>419116</t>
   </si>
   <si>
-    <t>刘畅</t>
+    <t>刘老师</t>
   </si>
   <si>
     <t>管理员</t>
@@ -1229,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="17.5740740740741" customWidth="1"/>
@@ -1292,13 +1298,22 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2"/>
@@ -1524,6 +1539,11 @@
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
